--- a/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,42 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -894,7 +769,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1190,7 +1065,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1686,7 +1561,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1782,7 +1657,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1878,7 +1753,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2074,7 +1949,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2220,7 +2095,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2366,7 +2241,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2662,7 +2537,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3158,7 +3033,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3254,7 +3129,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3300,7 +3175,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3346,7 +3221,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3392,7 +3267,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3438,7 +3313,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3484,7 +3359,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -6506,1583 +6381,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Victoria Coast - A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>58 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>16 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>42 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-$3,120万
-$22,824/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-$3,210万
-$23,482/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>24/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-$3,481万
-$25,461/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-$3,050万
-$22,312/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-$3,363万
-$24,600/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-$3,000万
-$21,946/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (3房)
-$2,780万
-$20,396/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>14/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>13/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-$2,550万
-$18,654/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-$2,750万
-$20,117/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-$2,500万
-$18,288/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>4/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-$2,426万
-$17,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-$2,360万
-$17,264/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-$2,605万
-$19,112/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-$2,310万
-$16,901/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>1 | 1363呎 (2房)
-$2,481万
-$18,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>2 | 1367呎 (2房)
-$2,206万
-$16,134/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Victoria Coast - B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>60 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>60 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>24/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>14/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>13/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>4/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>1 | 1361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>2 | 1356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +137,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +212,54 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +636,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -6381,4 +6543,1583 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+$3120万
+$22,824/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+$3210万
+$23,482/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+$3481万
+$25,461/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+$3050万
+$22,312/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+$3363万
+$24,600/呎
+(23年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+$3000万
+$21,946/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (3房)
+$2780万
+$20,396/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+$2550万
+$18,654/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+$2750万
+$20,117/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+$2500万
+$18,288/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+$2426万
+$17,800/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+$2360万
+$17,264/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+$2605万
+$19,112/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+$2310万
+$16,901/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>1 | 1363呎 (2房)
+$2481万
+$18,200/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>2 | 1367呎 (2房)
+$2206万
+$16,134/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>1 | 1361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>2 | 1356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -636,7 +636,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -639,6 +639,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -696,6 +700,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -746,6 +770,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -796,6 +840,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -846,6 +910,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -896,6 +980,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -942,6 +1046,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -992,6 +1116,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1042,6 +1186,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1092,6 +1256,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1142,6 +1326,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1192,6 +1396,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1238,6 +1462,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1288,6 +1532,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1338,6 +1602,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1388,6 +1672,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1438,6 +1742,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1488,6 +1812,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1538,6 +1882,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1588,6 +1952,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1638,6 +2022,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1688,6 +2092,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1734,6 +2158,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1784,6 +2228,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1830,6 +2294,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1880,6 +2364,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1926,6 +2430,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1976,6 +2500,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2026,6 +2570,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2076,6 +2640,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2122,6 +2706,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2172,6 +2776,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2222,6 +2846,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2268,6 +2912,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2318,6 +2982,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2368,6 +3052,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2414,6 +3118,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2464,6 +3188,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2514,6 +3258,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2564,6 +3328,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2614,6 +3398,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2664,6 +3468,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2710,6 +3534,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2760,6 +3604,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2810,6 +3674,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2860,6 +3744,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2910,6 +3814,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2960,6 +3884,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3010,6 +3954,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3060,6 +4024,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3110,6 +4094,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3160,6 +4164,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3206,6 +4230,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3256,6 +4300,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3302,6 +4366,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3348,6 +4432,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3394,6 +4498,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3440,6 +4564,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3486,6 +4630,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3532,6 +4696,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3582,6 +4766,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3632,6 +4836,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3682,6 +4906,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3732,6 +4976,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3782,6 +5046,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3832,6 +5116,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3882,6 +5186,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3932,6 +5256,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3982,6 +5326,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4032,6 +5396,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4082,6 +5466,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4132,6 +5536,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4182,6 +5606,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4232,6 +5676,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4282,6 +5746,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4332,6 +5816,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4382,6 +5886,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4432,6 +5956,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4482,6 +6026,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4532,6 +6096,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4582,6 +6166,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4632,6 +6236,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4682,6 +6306,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4732,6 +6376,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4782,6 +6446,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4832,6 +6516,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4882,6 +6586,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4932,6 +6656,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4982,6 +6726,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5032,6 +6796,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5082,6 +6866,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5132,6 +6936,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5182,6 +7006,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5232,6 +7076,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5282,6 +7146,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5332,6 +7216,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5382,6 +7286,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5432,6 +7356,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5482,6 +7426,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5532,6 +7496,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5582,6 +7566,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5632,6 +7636,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5682,6 +7706,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5732,6 +7776,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5782,6 +7846,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5832,6 +7916,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5882,6 +7986,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5932,6 +8056,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5982,6 +8126,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6032,6 +8196,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6082,6 +8266,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6132,6 +8336,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6182,6 +8406,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6232,6 +8476,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6282,6 +8546,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6332,6 +8616,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6382,6 +8686,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6432,6 +8756,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6482,6 +8826,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6532,13 +8896,33 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6712,7 +9096,7 @@
           <t>2 | 1367呎 (3房)
 $3120万
 $22,824/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -6781,7 +9165,7 @@
           <t>2 | 1367呎 (3房)
 $3210万
 $23,482/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -6896,7 +9280,7 @@
           <t>2 | 1367呎 (3房)
 $3481万
 $25,461/呎
-(23年-10月)</t>
+(23年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -6919,7 +9303,7 @@
           <t>2 | 1367呎 (3房)
 $3050万
 $22,312/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -6942,7 +9326,7 @@
           <t>2 | 1367呎 (3房)
 $3363万
 $24,600/呎
-(23年-11月)</t>
+(23年-11月-16日)</t>
         </is>
       </c>
     </row>
@@ -6988,7 +9372,7 @@
           <t>2 | 1367呎 (3房)
 $3000万
 $21,946/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -7003,7 +9387,7 @@
           <t>1 | 1363呎 (3房)
 $2780万
 $20,396/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -7057,7 +9441,7 @@
           <t>2 | 1367呎 (2房)
 $2550万
 $18,654/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -7126,7 +9510,7 @@
           <t>2 | 1367呎 (2房)
 $2750万
 $20,117/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -7241,7 +9625,7 @@
           <t>2 | 1367呎 (2房)
 $2500万
 $18,288/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -7256,7 +9640,7 @@
           <t>1 | 1363呎 (2房)
 $2426万
 $17,800/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -7264,7 +9648,7 @@
           <t>2 | 1367呎 (2房)
 $2360万
 $17,264/呎
-(24年-12月)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -7279,7 +9663,7 @@
           <t>1 | 1363呎 (2房)
 $2605万
 $19,112/呎
-(23年-10月)</t>
+(23年-10月-26日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -7287,7 +9671,7 @@
           <t>2 | 1367呎 (2房)
 $2310万
 $16,901/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -7302,7 +9686,7 @@
           <t>1 | 1363呎 (2房)
 $2481万
 $18,200/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -7310,7 +9694,7 @@
           <t>2 | 1367呎 (2房)
 $2206万
 $16,134/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -9096,7 +9096,7 @@
           <t>2 | 1367呎 (3房)
 $3120万
 $22,824/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
           <t>2 | 1367呎 (3房)
 $3210万
 $23,482/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9280,7 @@
           <t>2 | 1367呎 (3房)
 $3481万
 $25,461/呎
-(23年-10月-29日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
           <t>2 | 1367呎 (3房)
 $3050万
 $22,312/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
           <t>2 | 1367呎 (3房)
 $3363万
 $24,600/呎
-(23年-11月-16日)</t>
+(23年-11月)</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
           <t>2 | 1367呎 (3房)
 $3000万
 $21,946/呎
-(24年-06月-03日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
           <t>1 | 1363呎 (3房)
 $2780万
 $20,396/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9441,7 +9441,7 @@
           <t>2 | 1367呎 (2房)
 $2550万
 $18,654/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
           <t>2 | 1367呎 (2房)
 $2750万
 $20,117/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9625,7 @@
           <t>2 | 1367呎 (2房)
 $2500万
 $18,288/呎
-(24年-12月-11日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
           <t>1 | 1363呎 (2房)
 $2426万
 $17,800/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -9648,7 +9648,7 @@
           <t>2 | 1367呎 (2房)
 $2360万
 $17,264/呎
-(24年-12月-18日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9663,7 @@
           <t>1 | 1363呎 (2房)
 $2605万
 $19,112/呎
-(23年-10月-26日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -9671,7 +9671,7 @@
           <t>2 | 1367呎 (2房)
 $2310万
 $16,901/呎
-(24年-08月-08日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
           <t>1 | 1363呎 (2房)
 $2481万
 $18,200/呎
-(23年-10月-18日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -9694,7 +9694,7 @@
           <t>2 | 1367呎 (2房)
 $2206万
 $16,134/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -9096,7 +9096,7 @@
           <t>2 | 1367呎 (3房)
 $3120万
 $22,824/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
           <t>2 | 1367呎 (3房)
 $3210万
 $23,482/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9280,7 @@
           <t>2 | 1367呎 (3房)
 $3481万
 $25,461/呎
-(23年-10月)</t>
+(23年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
           <t>2 | 1367呎 (3房)
 $3050万
 $22,312/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
           <t>2 | 1367呎 (3房)
 $3363万
 $24,600/呎
-(23年-11月)</t>
+(23年-11月-16日)</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
           <t>2 | 1367呎 (3房)
 $3000万
 $21,946/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
           <t>1 | 1363呎 (3房)
 $2780万
 $20,396/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9441,7 +9441,7 @@
           <t>2 | 1367呎 (2房)
 $2550万
 $18,654/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
           <t>2 | 1367呎 (2房)
 $2750万
 $20,117/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9625,7 @@
           <t>2 | 1367呎 (2房)
 $2500万
 $18,288/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
           <t>1 | 1363呎 (2房)
 $2426万
 $17,800/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -9648,7 +9648,7 @@
           <t>2 | 1367呎 (2房)
 $2360万
 $17,264/呎
-(24年-12月)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9663,7 @@
           <t>1 | 1363呎 (2房)
 $2605万
 $19,112/呎
-(23年-10月)</t>
+(23年-10月-26日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -9671,7 +9671,7 @@
           <t>2 | 1367呎 (2房)
 $2310万
 $16,901/呎
-(24年-08月)</t>
+(24年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
           <t>1 | 1363呎 (2房)
 $2481万
 $18,200/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -9694,7 +9694,7 @@
           <t>2 | 1367呎 (2房)
 $2206万
 $16,134/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
     </row>
